--- a/Лист1_три_колонки_РТН_и_сайт.xlsx
+++ b/Лист1_три_колонки_РТН_и_сайт.xlsx
@@ -30,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
@@ -70,10 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -91,6 +98,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -464,63 +474,63 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Три колонки вопросов</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>1 (синий) — ваши вопросы из Лист1</t>
+          <t>Три колонки + цвета как в первой таблице</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2 (зелёный) — формулировки из официального перечня Ростехнадзора 2026 (лист III — потребители тепловой энергии)</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Синий — ваши вопросы (Лист1)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3 (оранжевый) — формулировки с сайта prombez24.com (тесты отопления/вентиляции/потребителей)</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Зелёный — точное совпадение с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Жёлтый — аналог / другая формулировка в банке РТН</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Всего: 93</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Серый — прямого аналога в банке РТН нет (иногда показан ближайший для справки)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>С банком РТН сопоставлено: 35 (уверенных: 24)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>С сайтом: 93</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Оранжевый — формулировка с сайта prombez24.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Всего: 93; exact=21; analog=11; none=61</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Источник банка РТН: Перечень_тестовых_вопросов_с_ответами_2026(31.03).xlsx, лист III</t>
+          <t>Колонка 2 (E) — как в файле «Лист1_со_старыми_и_новыми_формулировками»: аналоги и иные формулировки из банка РТН</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Источник сайта: https://prombez24.com/tests/301 , /300 , /464</t>
+          <t>Колонка 3 (I) — вопросы с сайта</t>
         </is>
       </c>
     </row>
@@ -535,3542 +545,4575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>1. Ваш вопрос (Лист1)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Код</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>2. Вопрос Ростехнадзор (банк 2026, лист III)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Примечание по банку РТН</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Статус сопоставления с РТН</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>2. Вопрос Ростехнадзор (банк 2026) — аналоги и формулировки</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Лист / № в банке РТН</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Сходство</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Комментарий по РТН</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>3. Вопрос с сайта prombez24.com</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Раздел на сайте</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Ссылка на сайт</t>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
         </is>
       </c>
     </row>
     <row r="2" ht="55" customHeight="1">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью должны пересматриваться перечни оперативной документации?</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью должны пересматриваться перечни оперативной документации?</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="3" ht="55" customHeight="1">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Когда проводятся испытания систем воздушного отопления и приточной вентиляции по определению эффективности работы установок и соответствия их паспортным и проектным данным?</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>Когда проводятся испытания систем воздушного отопления и приточной вентиляции по определению эффективности работы установок и соответствия их паспортным и проектным данным?</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="4" ht="55" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Где проводится проверка знаний ответственных за исправное состояние и безопасную эксплуатацию тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
           <t>Какое мероприятие не должен обеспечить ответственный за исправное состояние и безопасную эксплуатацию объектов теплоснабжения и теплопотребляющих установок в пределах своих полномочий, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>III №8 — слабый аналог (37%)</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>III №8</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Где проводится проверка знаний ответственных за исправное состояние и безопасную эксплуатацию тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="5" ht="55" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Какая арматура может использоваться в качестве запорной арматуры с Dу до 50 мм в системах горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>В каком случае допускается использование запорной арматуры в качестве регулирующей, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>III №236</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 60%)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Какая арматура может использоваться в качестве запорной арматуры с Dу до 50 мм в системах горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью должна проводиться очистка внутренних частей воздуховодов систем вентиляции?</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью должна проводиться очистка внутренних частей воздуховодов систем вентиляции?</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Где теплоснабжающие организации должны утвердить график ограничений отпуска тепловой энергии в случае принятия неотложных мер по предотвращению или ликвидации аварий в системе теплоснабжения?</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Где теплоснабжающие организации должны утвердить график ограничений отпуска тепловой энергии в случае принятия неотложных мер по предотвращению или ликвидации аварий в системе теплоснабжения?</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Когда заканчивается отопительный период?</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Когда заканчивается отопительный период?</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Когда проводится промывка систем отопления?</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Когда проводится промывка систем отопления?</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Каким образом оформляется допуск персонала к самостоятельной работе на тепловых энергоустановках?</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Каким образом оформляется допуск персонала к самостоятельной работе на тепловых энергоустановках?</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>С кем должен быть согласован график включения и отключения систем теплопотребления согласно правилам по технической эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>С кем должен быть согласован график включения и отключения систем теплопотребления согласно правилам по технической эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Электрооборудование тепловых энергоустановок должно соответствовать:</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Электрооборудование тепловых энергоустановок должно соответствовать:</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="13" ht="55" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью должен проводиться повторный инструктаж по безопасности труда для персонала, обслуживающего тепловые энергоустановки?</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>С какой периодичностью проводятся плановые производственные инструктажи, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>III №72</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 55%)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью должен проводиться повторный инструктаж по безопасности труда для персонала, обслуживающего тепловые энергоустановки?</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="14" ht="55" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Каким пробным давлением проводятся испытания на прочность и плотность систем горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Какие действия выполняются если результаты испытаний на прочность и плотность трубопроводов и оборудования теплопотребляющих установок, работающего под избыточным давлением не удовлетворяют условиям прохождения таких испытаний, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>III №250</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 58%)</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Каким пробным давлением проводятся испытания на прочность и плотность систем горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Какой толщины должны быть тепловая изоляция подающих трубопроводов систем горячего водоснабжения, за исключением подводок к водоразборным приборам?</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Какой толщины должна быть тепловая изоляция подающих трубопроводов систем горячего водоснабжения, за исключением подводок к водоразборным приборам?</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="16" ht="55" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью управленческий персонал и специалисты организации должны проводить осмотры тепловых пунктов?</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью управленческий персонал и специалисты организации должны проводить осмотры тепловых пунктов?</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Допускается ли прокладывать трубы с легковоспламеняющимися и горючими жидкостями и газами через помещение для вентиляционного оборудования?</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Допускается ли прокладывать трубы с легковоспламеняющимися и горючими жидкостями и газами через помещение для вентиляционного оборудования?</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="18" ht="55" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Кто из специалистов организации может быть назначен ответственным за исправное состояние и безопасную эксплуатацию тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
           <t>Какое утверждение относительно осуществления ответственным за исправное состояние и безопасную эксплуатацию наружного и внутреннего осмотра котла, является неверным и противоречит Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>III №173 — слабый аналог (38%)</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>III №173</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Кто из специалистов организации может быть назначен ответственным за исправное состояние и безопасную эксплуатацию тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="19" ht="55" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>В каком случае ответственность за исправное состояние и безопасную эксплуатацию тепловых энергоустановок может быть возложена на работника, не имеющего теплоэнергетического образования?</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
           <t>Какое мероприятие не должен обеспечить ответственный за исправное состояние и безопасную эксплуатацию объектов теплоснабжения и теплопотребляющих установок в пределах своих полномочий, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>III №8 — слабый аналог (41%)</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>III №8</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>В каком случае ответственность за исправное состояние и безопасную эксплуатацию тепловых энергоустановок может быть возложена на работника, не имеющего теплоэнергетического образования?</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="20" ht="55" customHeight="1">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>При каком условии производится включение в работу тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>При каком условии производится включение в работу тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="21" ht="55" customHeight="1">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью необходимо производить замену уплотняющих прокладок фланцевых соединений систем отопления?</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью необходимо производить замену уплотняющих прокладок фланцевых соединений систем отопления?</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="22" ht="55" customHeight="1">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Какими документами определяется территория для размещения производственных зданий и сооружений тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Какими документами определяется территория для размещения производственных зданий и сооружений тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="23" ht="55" customHeight="1">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Когда начинается отопительный период?</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Когда начинается отопительный период?</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="24" ht="55" customHeight="1">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Какая минимальная продолжительность дублирования после проверки знаний установлена для оперативных руководителей тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Какова периодичность проверки знаний работников при производстве работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>III №2</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Какая минимальная продолжительность дублирования после проверки знаний установлена для оперативных руководителей тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="25" ht="55" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Что из перечисленного не входит в состав необходимой документации при эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Что из перечисленного не входит в состав необходимой документации при эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="26" ht="55" customHeight="1">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Какое освещение должны иметь приточные камеры систем вентиляции?</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Какое освещение должны иметь приточные камеры систем вентиляции?</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="27" ht="55" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Кем осуществляется техническое обслуживание и ремонт средств измерений теплотехнических параметров тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Кем осуществляются техническое обслуживание и ремонт средств измерений теплотехнических параметров тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Какая система отопления оборудуется приборами автоматического регулирования расхода тепловой энергии и теплоносителя?</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Какая система отопления оборудуется приборами автоматического регулирования расхода тепловой энергии и теплоносителя?</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="29" ht="55" customHeight="1">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Какой документ должен быть составлен на каждый тепловой пункт?</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Какой документ должен быть составлен на каждый тепловой пункт?</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="30" ht="55" customHeight="1">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Какой должна быть температура поверхности тепловой изоляции теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Какую температуру наружной поверхности элементов теплоснабжения, теплопотребляющих установок должна обеспечивать тепловая изоляция?</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>III №8 (сходство 58%)</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>III №8</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 65%)</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Какой должна быть температура поверхности тепловой изоляции теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="31" ht="55" customHeight="1">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Кто проводит периодические осмотры тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Кто проводит периодические осмотры тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="32" ht="55" customHeight="1">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Правила технической эксплуатации тепловых энергоустановок устанавливают требования по технической эксплуатации следующих тепловых энергоустановок:</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Какие обязательные требования не устанавливаются Правилами технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>III №1 — слабый аналог (37%)</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Правила технической эксплуатации тепловых энергоустановок устанавливают требования по технической эксплуатации следующих тепловых энергоустановок:</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="33" ht="55" customHeight="1">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Какова периодичность и сроки проведения текущего ремонта систем теплопотребления?</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
           <t>Какова периодичность проверки знаний работников при производстве работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>III №2 — слабый аналог (37%)</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>III №2</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Каковы периодичность и сроки проведения текущего ремонта систем теплопотребления?</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="34" ht="55" customHeight="1">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью необходимо проводить осмотры разводящих трубопроводов систем отопления, расположенных в подвалах?</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью необходимо проводить осмотры разводящих трубопроводов систем отопления, расположенных в подвалах?</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="35" ht="55" customHeight="1">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Какие требования предъявляются к трубопроводам, проложенным в подвалах и других неотапливаемых помещениях?</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
           <t>Какие требования предъявляются к работникам при выполнении работ по эксплуатации по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>III №1 — слабый аналог (40%)</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>III №1</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Какие требования предъявляются к трубопроводам систем отопления, проложенным в подвалах и других неотапливаемых помещениях?</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="36" ht="55" customHeight="1">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Кем выдается разрешение на включение или отключение тепловых пунктов и систем теплопотребления?</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Кем выдается разрешение на включение или отключение тепловых пунктов и систем теплопотребления?</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="37" ht="55" customHeight="1">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью нужно проводить осмотры оборудования систем приточной вентиляции?</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью нужно проводить осмотры оборудования систем приточной вентиляции?</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="38" ht="55" customHeight="1">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Что из перечисленного не указывается в инструкции по эксплуатации тепловой энергоустановки?</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Что из перечисленного не указывается в инструкции по эксплуатации тепловой энергоустановки?</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="39" ht="55" customHeight="1">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>На кого возложена ответственность за обеспечение пожарной безопасности помещений и оборудования тепловых энергоустановок, а также за наличие и исправное состояние первичных средств пожаротушения?</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>На кого возложена ответственность за обеспечение пожарной безопасности помещений и оборудования тепловых энергоустановок, а также за наличие и исправное состояние первичных средств пожаротушения?</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="40" ht="55" customHeight="1">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Что из перечисленного не указывается в должностной инструкции персонала?</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Что из перечисленного не указывается в должностной инструкции персонала?</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="41" ht="55" customHeight="1">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Какая вода используется для промывания систем отопления?</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Какая вода используется для промывания систем отопления?</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="42" ht="55" customHeight="1">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Периодичность участия оперативных руководителей в контрольных противопожарных тренировках?</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Периодичность участия оперативных руководителей в контрольных противопожарных тренировках?</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="43" ht="55" customHeight="1">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Кто определяет порядок организации и проведения обходов и осмотров рабочих мест?</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Какие положения не должен содержать порядок организации и проведения обходов и осмотров рабочих мест, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>III №10 (сходство 60%)</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>III №10</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 89%)</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Кто определяет порядок организации и проведения обходов и осмотров рабочих мест?</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="44" ht="55" customHeight="1">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>В течение какого времени проводится стажировка для ремонтного, оперативного, оперативно-ремонтного персонала при назначении на должность?</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Каким образом устанавливается продолжительность стажировки, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>III №60</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 55%)</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>В течение какого времени проводится стажировка для ремонтного, оперативного, оперативно-ремонтного персонала при назначении на должность?</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="45" ht="55" customHeight="1">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Какова допустимая норма часовой утечки теплоносителя из систем отопления, вентиляции и горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Какова допустимая норма часовой утечки теплоносителя из систем отопления, вентиляции и горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="46" ht="55" customHeight="1">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Какие водоподогреватели не применяются в тепловых пунктах?</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Какие водоподогреватели не применяются в тепловых пунктах?</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="47" ht="55" customHeight="1">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>С какой целью проводится входной контроль металла?</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>С какой целью проводится входной контроль металла?</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Вентиляция (ЭБП 1492.6)</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/300</t>
         </is>
       </c>
     </row>
     <row r="48" ht="55" customHeight="1">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>С какой целью проводится эксплуатационный контроль металла?</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>С какой целью проводится эксплуатационный контроль металла?</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="49" ht="55" customHeight="1">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Какие мероприятия из перечисленных не входят в комплекс мероприятий при подготовке к отопительному периоду для обеспечения надежности теплоснабжения потребителей?</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Какие работы не должны выполняться в тепловых пунктах в период подготовки к отопительному периоду, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>III №225</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 55%)</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Какие мероприятия из перечисленных не входят в комплекс мероприятий при подготовке к отопительному периоду для обеспечения надежности теплоснабжения потребителей?</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="50" ht="55" customHeight="1">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>В каком случае проводятся внеочередные испытания на прочность и плотность теплопотребляющих энергоустановок?</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>В каком случае при техническом освидетельствовании допускается замещение наружного и внутреннего осмотра, гидравлического испытания на прочность и плотность методами неразрушающего контроля технического состояния, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>III №32 — слабый аналог (40%)</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Какие действия выполняются если результаты испытаний на прочность и плотность трубопроводов и оборудования теплопотребляющих установок, работающего под избыточным давлением не удовлетворяют условиям прохождения таких испытаний, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>III №250</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 55%)</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>В каком случае проводятся внеочередные испытания на прочность и плотность теплопотребляющих энергоустановок?</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="51" ht="55" customHeight="1">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Какой условный диаметр должна иметь запорная арматура штуцеров, устанавливаемых в низших точках трубопроводов воды и конденсата?</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Какой условный диаметр должна иметь запорная арматура штуцеров, устанавливаемых в низших точках трубопроводов воды и конденсата?</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="52" ht="55" customHeight="1">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Как долго хранятся документы, в которых регистрируются результаты контроля за металлом?</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr"/>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Как долго хранятся документы, в которых регистрируются результаты контроля за металлом?</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="53" ht="55" customHeight="1">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>На кого возложена ответственность за невыполнение Правил технической эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Какие обязательные требования не устанавливаются Правилами технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>III №1 — слабый аналог (35%)</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>На кого возложена ответственность за невыполнение Правил технической эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="54" ht="55" customHeight="1">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Какие заглушки не применяются в коллекторах диаметром более 500 мм?</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Какие заглушки не применяются в коллекторах диаметром более 500 мм?</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="55" ht="55" customHeight="1">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>В каких пределах допускается отклонение среднесуточной температуры воды, поступившей в систему отопления и горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>В каких пределах допускается отклонение среднесуточной температуры воды, поступившей в систему отопления и горячего водоснабжения?</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="56" ht="55" customHeight="1">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Какие сведения не указываются на табличке теплопотребляющей энергоустановки, работающей под давлением, после ее установки и регистрации?</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>Какие сведения не указываются на табличке теплопотребляющей энергоустановки, работающей под давлением, после ее установки и регистрации?</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="57" ht="55" customHeight="1">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Кем утверждаются планы ППР тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>Кем утверждаются ППР тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="58" ht="55" customHeight="1">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Какой срок хранения предусмотрен для исполнительных схем-генпланов подземных сооружений и коммуникаций на территории организации?</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Какой срок хранения предусмотрен для исполнительных схем-генпланов подземных сооружений и коммуникаций на территории организации?</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="59" ht="55" customHeight="1">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>В каком случае не проводится внеочередная проверка знаний?</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>В каком случае не проводится первичная проверка знаний документов, знание которых обязательно для работы в данной должности (профессии), у работников, эксплуатирующих объекты теплоснабжения и (или) теплопотребляющие установки, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>III №63 — слабый аналог (40%)</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Какое условие проведения внеочередной проверки знаний работников, независимо от срока проведения предыдущей проверки, является неверным и противоречит Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>III №66</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 55%)</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>В каком случае не проводится внеочередная проверка знаний?</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="60" ht="55" customHeight="1">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>При каком перерыве в работе по специальности необходимо проходить переподготовку персоналу, связанному с эксплуатацией тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>При каком перерыве в работе по специальности необходимо проходить переподготовку персоналу, связанному с эксплуатацией тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="61" ht="55" customHeight="1">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>В течение какого срока должны храниться записи показаний регистрирующих приборов?</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>В течение какого срока должны храниться записи показаний регистрирующих приборов?</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="62" ht="55" customHeight="1">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью необходимо осуществлять очистку наружных поверхностей нагревательных приборов от пыли и грязи?</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью необходимо осуществлять очистку наружных поверхностей нагревательных приборов от пыли и грязи?</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="63" ht="55" customHeight="1">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Что не входит в обязательные формы работы с управленческим персоналом и специалистами при эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>Что не входит в обязательные формы работы с управленческим персоналом и специалистами при эксплуатации тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="64" ht="55" customHeight="1">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Кто утверждает графики проверки знаний персонала, эксплуатирующего тепловые энергоустановки?</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
           <t>Какова периодичность проверки знаний работников при производстве работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>III №2 — слабый аналог (38%)</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>III №2</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>Кто утверждает графики проверки знаний персонала, эксплуатирующего тепловые энергоустановки?</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="65" ht="55" customHeight="1">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Для чего на шкалу манометра теплопотребляющей установки наносится красная черта?</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>Для чего на шкалу манометра теплопотребляющей установки наносится красная черта?</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="66" ht="55" customHeight="1">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Где должны храниться схемы тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>Где должны храниться схемы тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="67" ht="55" customHeight="1">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>За сколько дней до проведения пробной топки перед началом отопительного периода теплоснабжающая организация должна уведомить об этом потребителей?</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>За сколько дней до проведения пробной топки перед началом отопительного периода теплоснабжающая организация должна уведомить об этом потребителей?</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="68" ht="55" customHeight="1">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Что из перечисленного не относится к обязанностям ответственного за исправное состояние и безопасную эксплуатацию тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>АЭБ-29</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Какие меры должны быть приняты по требованию ответственного за исправное состояние и безопасную эксплуатацию если имеются признаки, указывающие на возможное наличие под футеровкой, обмуровкой и изоляцией дефектов, влияющих на безопасность оборудования, работающего под избыточным давлением, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>III №38 — слабый аналог (36%)</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Какое мероприятие не должен обеспечить ответственный за исправное состояние и безопасную эксплуатацию объектов теплоснабжения и теплопотребляющих установок в пределах своих полномочий, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>III №8</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Прямого аналога нет. Показан ближайший по словам из банка РТН — для справки.</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>Что из перечисленного не относится к обязанностям ответственного за исправное состояние и безопасную эксплуатацию тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="69" ht="55" customHeight="1">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Правила технической эксплуатации тепловых энергоустановок не распространяются на следующие виды тепловых энергоустановок:</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>Правила технической эксплуатации тепловых энергоустановок не распространяются на следующие виды тепловых энергоустановок:</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="70" ht="55" customHeight="1">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>В каком случае проводится внеочередное техническое освидетельствование тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>В каком случае не должно проводиться внеочередное техническое освидетельствование металлоконструкций котла, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>III №178 (сходство 51%)</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>III №178</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 79%)</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>В каком случае проводится внеочередное освидетельствование тепловых энергоустановок?</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="71" ht="55" customHeight="1">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Можно ли осуществлять разбор сетевой воды из закрытых систем теплоснабжения?</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>Можно ли осуществлять разбор сетевой воды из закрытых систем теплоснабжения?</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="72" ht="55" customHeight="1">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>С какой периодичностью организация должна проводить режимно-наладочные испытания и работы для разработки режимных карт и нормативных характеристик работы элементов системы теплоснабжения?</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Аналог в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>Какие инструкции не пересматриваются и не переутверждаются по результатам режимно-наладочных испытаний и наладки водно-химических режимов водоподготовительных установок, согласно Правилам технической эксплуатации объектов теплоснабжения и теплопотребляющих установок, утвержденным приказом Минэнерго России от 14.05.2025 № 511?</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>III №195</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Ближайший аналог в банке РТН (лист III, сходство 55%)</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>С какой периодичностью организация должна проводить режимно-наладочные испытания и работы для разработки режимных карт и нормативных характеристик работы элементов системы теплоснабжения?</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="73" ht="55" customHeight="1">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>Из какого материала должна быть изготовлена запорная арматура, применяемая в качестве отключающей на вводе тепловых сетей в тепловой пункт?</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>В банке Ростехнадзора 2026 (лист III) не найден</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Аналог не найден</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Актуальной формулировки в банке Ростехнадзора 2026 не найдено</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>Из какого материала должна быть изготовлена запорная арматура, применяемая в качестве отключающей на вводе тепловых сетей в тепловой пункт?</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="74" ht="55" customHeight="1">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>Какую температуру наружной поверхности элементов теплоснабжения, теплопотребляющих установок должна обеспечивать тепловая изоляция?</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>Какую температуру наружной поверхности элементов теплоснабжения, теплопотребляющих установок должна обеспечивать тепловая изоляция?</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>III №8 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>III №8</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>Какую температуру наружной поверхности элементов теплоснабжения, теплопотребляющих установок должна обеспечивать тепловая изоляция?</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="75" ht="55" customHeight="1">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Какова периодичность проверки знаний работников при производстве работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>Какова периодичность проверки знаний работников при производстве работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>III №2 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>III №2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>Какова периодичность проверки знаний работников при производстве работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="76" ht="55" customHeight="1">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Каким напряжением должны использоваться светильники во взрывозащищенном исполнении при газоопасных работах?</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>Каким напряжением должны использоваться светильники во взрывозащищенном исполнении при газоопасных работах?</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>III №7 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>III №7</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>Каким напряжением должны использоваться светильники во взрывозащищенном исполнении при газоопасных работах?</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="77" ht="55" customHeight="1">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Кем утверждается и может быть дополнен перечень работ, выполняемых по нарядам-допускам?</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>Кем утверждается и может быть дополнен перечень работ, выполняемых по нарядам-допускам?</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>III №5 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>III №5</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>Кем утверждается и может быть дополнен перечень работ, выполняемых по нарядам-допускам?</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="78" ht="55" customHeight="1">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Какой документ оформляется при выполнении ремонтных и других работ подрядными, сервисными организациями на весь период выполнения работ на территории организации?</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
         <is>
           <t>Какой документ оформляется при выполнении ремонтных и других работ подрядными, сервисными организациями на весь период выполнения работ на территории организации?</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>III №6 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>III №6</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>Какой документ оформляется при выполнении ремонтных и других работ подрядными, сервисными организациями на весь период выполнения работ на территории организации?</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="79" ht="55" customHeight="1">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Что запрещается в помещении котельной при наличии признаков загазованности?</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>Что запрещается в помещении котельной при наличии признаков загазованности?</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>III №9 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>III №9</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>Что запрещается в помещении котельной при наличии признаков загазованности?</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="80" ht="55" customHeight="1">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Кто допускается к выполнению работ по техническому обслуживанию и ремонту объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>Кто допускается к выполнению работ по техническому обслуживанию и ремонту объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>III №3 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>III №3</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>Кто допускается к выполнению работ по техническому обслуживанию и ремонту объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="81" ht="55" customHeight="1">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>В соответствии с чем выполняются работы повышенной опасности в процессе технического обслуживания и ремонта объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>В соответствии с чем выполняются работы повышенной опасности в процессе технического обслуживания и ремонта объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>III №4 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>III №4</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>В соответствии с чем выполняются работы повышенной опасности в процессе технического обслуживания и ремонта объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="82" ht="55" customHeight="1">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Какие требования предъявляются к работникам при выполнении работ по эксплуатации по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>Какие требования предъявляются к работникам при выполнении работ по эксплуатации по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>III №1 (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>III №1</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>Какие требования предъявляются к работникам при выполнении работ по эксплуатации объектов теплоснабжения и теплопотребляющих установок?</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="83" ht="55" customHeight="1">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Как определяется первоочередность оказания первой помощи двум и более пострадавшим?</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>Как определяется первоочередность оказания первой помощи двум и более пострадавшим, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>III №10 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>III №10</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>Как определяется первоочередность оказания первой помощи двум и более пострадавшим, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="84" ht="55" customHeight="1">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Какие средства могут использоваться при оказании первой помощи?</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>Какие средства могут использоваться при оказании первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>III №11 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>III №11</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>Какие средства могут использоваться при оказании первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="85" ht="55" customHeight="1">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Допускается ли оказание помощи пострадавшему в принятии лекарственных препаратов для медицинского применения, назначенных ему ранее лечащим врачом.?</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>Допускается ли оказание помощи пострадавшему в принятии лекарственных препаратов для медицинского применения, назначенных ему ранее лечащим врачом, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>III №12 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>III №12</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>Допускается ли оказание помощи пострадавшему в принятии лекарственных препаратов для медицинского применения, назначенных ему ранее лечащим врачом, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="86" ht="55" customHeight="1">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при наличии у пострадавшего признаков жизни (дыхания, кровообращения) и отсутствии сознания.</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при наличии у пострадавшего признаков жизни (дыхания, кровообращения) и отсутствии сознания, в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>III №4 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при отсутствии у пострадавшего признаков жизни (дыхания, кровообращения), в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>III №3</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при наличии у пострадавшего признаков жизни (дыхания, кровообращения) и отсутствии сознания, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="87" ht="55" customHeight="1">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Перечислите способы по временной остановке наружного кровотечения.</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Перечислите способы по временной остановке наружного кровотечения, в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>III №7 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>III №7</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>Перечислите способы по временной остановке наружного кровотечения, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="88" ht="55" customHeight="1">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Укажите перечень исчерпывающих мероприятий по оказанию первой помощи.</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
         <is>
           <t>Укажите перечень исчерпывающих мероприятий по оказанию первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>III №1 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>III №1</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>Укажите перечень исчерпывающих мероприятий по оказанию первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="89" ht="55" customHeight="1">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>В каком случае допускается оказание первой помощи?</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>В каком случае допускается оказание первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>III №9 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>III №9</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
         <is>
           <t>В каком случае допускается оказание первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="90" ht="55" customHeight="1">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>Укажите верный перечень исчерпывающих мероприятий по проведению оценки обстановки и обеспечению безопасных условий для оказания первой помощи.</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>Укажите верный перечень исчерпывающих мероприятий по проведению оценки обстановки и обеспечению безопасных условий для оказания первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>III №2 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>III №2</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
         <is>
           <t>Укажите верный перечень исчерпывающих мероприятий по проведению оценки обстановки и обеспечению безопасных условий для оказания первой помощи, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="91" ht="55" customHeight="1">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при отсутствии у пострадавшего признаков жизни (дыхания, кровообращения)</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при отсутствии у пострадавшего признаков жизни (дыхания, кровообращения), в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>III №3 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>III №3</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
         <is>
           <t>Укажите последовательность действий по проведению сердечно-легочной реанимации и поддержанию проходимости дыхательных путей при отсутствии у пострадавшего признаков жизни (дыхания, кровообращения), в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="92" ht="55" customHeight="1">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Перечислите действия при проведении подробного осмотра и опроса пострадавшего (при наличии сознания) для выявления признаков травм, ранений, отравлений, укусов или ужаливаний ядовитых животных, поражений, вызванных механическими, химическими, электрическими, термическими поражающими факторами, воздействием излучения, и других состояний, угрожающих его жизни и здоровью</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
         <is>
           <t>Перечислите действия при проведении подробного осмотра и опроса пострадавшего (при наличии сознания) для выявления признаков травм, ранений, отравлений, укусов или ужаливаний ядовитых животных, поражений, вызванных механическими, химическими, электрическими, термическими поражающими факторами, воздействием излучения, и других состояний, угрожающих его жизни и здоровью, в соответствии с приказом Минздрава России от 03.05.2024 № 220н.</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>III №6 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr">
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>III №6</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>Перечислите действия при проведении подробного осмотра и опроса пострадавшего (при наличии сознания) для выявления признаков травм, ранений, отравлений, укусов или ужаливаний ядовитых животных, поражений, вызванных механическими, химическими, электрическими, термическими поражающими факторами, воздействием излучения, и других состояний, угрожающих его жизни и здоровью, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="93" ht="55" customHeight="1">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>Перечислите состояния, при которых не оказывается первая помощь в соответствии с Приказом Министерства здравоохранения Российской Федерации от 3 мая 2024 г. N 220н "Об утверждении Порядка оказания первой помощи"?</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
         <is>
           <t>Перечислите  состояния, при которых не оказывается первая помощь в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>III №5 (сходство 92%)</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>III №5</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>Перечислите состояния, при которых не оказывается первая помощь в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
       </c>
     </row>
     <row r="94" ht="55" customHeight="1">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Какие действия оказывающего помощь не относятся к мероприятиям по подробному осмотру и опросу пострадавшего в целях выявления признаков травм, ранений, отравлений, укусов или ужаливаний ядовитых животных, поражений, вызванных механическими, химическими, электрическими, термическими поражающими факторами, воздействием излучения, и других состояний, угрожающих его жизни и здоровью?</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>АЭБ-29</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>АЭБ-29</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Есть в банке РТН 2026</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t>Какие действия оказывающего помощь не относятся к мероприятиям по подробному осмотру и опросу пострадавшего в целях выявления признаков травм, ранений, отравлений, укусов или ужаливаний ядовитых животных, поражений, вызванных механическими, химическими, электрическими, термическими поражающими факторами, воздействием излучения, и других состояний, угрожающих его жизни и здоровью, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>III №8 (сходство 95%)</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>III №8</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Совпадает с банком Ростехнадзора 2026</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
         <is>
           <t>Какие действия оказывающего помощь не относятся к мероприятиям по подробному осмотру и опросу пострадавшего в целях выявления признаков травм, ранений, отравлений, укусов или ужаливаний ядовитых животных, поражений, вызванных механическими, химическими, электрическими, термическими поражающими факторами, воздействием излучения, и других состояний, угрожающих его жизни и здоровью, в соответствии с приказом Минздрава России от 03.05.2024 № 220н?</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Отопление (ЭБП 1493.6)</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>Отопление (ЭБП 1493.6)</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
         <is>
           <t>https://prombez24.com/tests/301</t>
         </is>
